--- a/output/yearly_population_iteration_31_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_31_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5483</v>
+        <v>5609</v>
       </c>
       <c r="C2" t="n">
-        <v>8427</v>
+        <v>6252</v>
       </c>
       <c r="D2" t="n">
-        <v>22358</v>
+        <v>37384</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3556</v>
+        <v>3504</v>
       </c>
       <c r="C3" t="n">
-        <v>6367</v>
+        <v>5713</v>
       </c>
       <c r="D3" t="n">
-        <v>12272</v>
+        <v>19269</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2504</v>
+        <v>2863</v>
       </c>
       <c r="C4" t="n">
-        <v>6812</v>
+        <v>5987</v>
       </c>
       <c r="D4" t="n">
-        <v>6994</v>
+        <v>8579</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1637</v>
+        <v>1796</v>
       </c>
       <c r="C5" t="n">
-        <v>5419</v>
+        <v>4620</v>
       </c>
       <c r="D5" t="n">
-        <v>2713</v>
+        <v>3156</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>910</v>
+        <v>944</v>
       </c>
       <c r="C6" t="n">
-        <v>3649</v>
+        <v>2901</v>
       </c>
       <c r="D6" t="n">
-        <v>1147</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>431</v>
+        <v>408</v>
       </c>
       <c r="C7" t="n">
-        <v>2194</v>
+        <v>1837</v>
       </c>
       <c r="D7" t="n">
-        <v>644</v>
+        <v>661</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="C8" t="n">
-        <v>1102</v>
+        <v>884</v>
       </c>
       <c r="D8" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C9" t="n">
-        <v>430</v>
+        <v>381</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -923,7 +923,7 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D12" t="n">
         <v>162</v>
@@ -937,7 +937,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
         <v>123</v>
@@ -951,7 +951,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
         <v>63</v>
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6084</v>
+        <v>5735</v>
       </c>
       <c r="C2" t="n">
-        <v>9493</v>
+        <v>5859</v>
       </c>
       <c r="D2" t="n">
-        <v>28550</v>
+        <v>35539</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3572</v>
+        <v>3601</v>
       </c>
       <c r="C3" t="n">
-        <v>6414</v>
+        <v>5247</v>
       </c>
       <c r="D3" t="n">
-        <v>12757</v>
+        <v>20437</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2513</v>
+        <v>2711</v>
       </c>
       <c r="C4" t="n">
-        <v>6399</v>
+        <v>5733</v>
       </c>
       <c r="D4" t="n">
-        <v>7524</v>
+        <v>10062</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1769</v>
+        <v>1980</v>
       </c>
       <c r="C5" t="n">
-        <v>5882</v>
+        <v>5096</v>
       </c>
       <c r="D5" t="n">
-        <v>3288</v>
+        <v>3862</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1112</v>
+        <v>1180</v>
       </c>
       <c r="C6" t="n">
-        <v>4395</v>
+        <v>3632</v>
       </c>
       <c r="D6" t="n">
-        <v>1346</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="C7" t="n">
-        <v>2799</v>
+        <v>2277</v>
       </c>
       <c r="D7" t="n">
-        <v>711</v>
+        <v>735</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="C8" t="n">
-        <v>1561</v>
+        <v>1285</v>
       </c>
       <c r="D8" t="n">
-        <v>451</v>
+        <v>461</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C9" t="n">
-        <v>695</v>
+        <v>579</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C10" t="n">
-        <v>303</v>
+        <v>279</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1217,7 +1217,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
         <v>184</v>
@@ -1237,7 +1237,7 @@
         <v>139</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1248,7 +1248,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
         <v>126</v>
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D16" t="n">
         <v>63</v>
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6964</v>
+        <v>6936</v>
       </c>
       <c r="C2" t="n">
-        <v>13153</v>
+        <v>5581</v>
       </c>
       <c r="D2" t="n">
-        <v>39180</v>
+        <v>36098</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3718</v>
+        <v>3630</v>
       </c>
       <c r="C3" t="n">
-        <v>6789</v>
+        <v>4883</v>
       </c>
       <c r="D3" t="n">
-        <v>13835</v>
+        <v>20941</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2517</v>
+        <v>2613</v>
       </c>
       <c r="C4" t="n">
-        <v>6210</v>
+        <v>5353</v>
       </c>
       <c r="D4" t="n">
-        <v>8048</v>
+        <v>11153</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1828</v>
+        <v>2020</v>
       </c>
       <c r="C5" t="n">
-        <v>5973</v>
+        <v>5204</v>
       </c>
       <c r="D5" t="n">
-        <v>3725</v>
+        <v>4637</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1244</v>
+        <v>1370</v>
       </c>
       <c r="C6" t="n">
-        <v>4899</v>
+        <v>4190</v>
       </c>
       <c r="D6" t="n">
-        <v>1576</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>691</v>
+        <v>716</v>
       </c>
       <c r="C7" t="n">
-        <v>3396</v>
+        <v>2784</v>
       </c>
       <c r="D7" t="n">
-        <v>790</v>
+        <v>836</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="C8" t="n">
-        <v>2033</v>
+        <v>1651</v>
       </c>
       <c r="D8" t="n">
-        <v>475</v>
+        <v>486</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C9" t="n">
-        <v>1001</v>
+        <v>841</v>
       </c>
       <c r="D9" t="n">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C10" t="n">
-        <v>438</v>
+        <v>381</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -1531,7 +1531,7 @@
         <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="D11" t="n">
         <v>207</v>
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1559,7 +1559,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
         <v>128</v>
@@ -1573,7 +1573,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1601,7 +1601,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
         <v>63</v>
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -1632,7 +1632,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6433</v>
+        <v>6360</v>
       </c>
       <c r="C2" t="n">
-        <v>9154</v>
+        <v>3839</v>
       </c>
       <c r="D2" t="n">
-        <v>32008</v>
+        <v>29883</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4456</v>
+        <v>4514</v>
       </c>
       <c r="C3" t="n">
-        <v>10508</v>
+        <v>7522</v>
       </c>
       <c r="D3" t="n">
-        <v>15089</v>
+        <v>22524</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1689</v>
+        <v>1866</v>
       </c>
       <c r="C4" t="n">
-        <v>9072</v>
+        <v>7925</v>
       </c>
       <c r="D4" t="n">
-        <v>7828</v>
+        <v>10485</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1149</v>
+        <v>1265</v>
       </c>
       <c r="C5" t="n">
-        <v>4801</v>
+        <v>4106</v>
       </c>
       <c r="D5" t="n">
-        <v>2545</v>
+        <v>3020</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>638</v>
+        <v>661</v>
       </c>
       <c r="C6" t="n">
-        <v>3328</v>
+        <v>2728</v>
       </c>
       <c r="D6" t="n">
-        <v>774</v>
+        <v>819</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C7" t="n">
-        <v>1992</v>
+        <v>1617</v>
       </c>
       <c r="D7" t="n">
-        <v>465</v>
+        <v>476</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C8" t="n">
-        <v>980</v>
+        <v>824</v>
       </c>
       <c r="D8" t="n">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>429</v>
+        <v>373</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10">
@@ -1828,7 +1828,7 @@
         <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
         <v>202</v>
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12">
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
         <v>125</v>
@@ -1870,7 +1870,7 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
         <v>98</v>
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -1898,7 +1898,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
         <v>61</v>
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
         <v>49</v>
@@ -1929,7 +1929,7 @@
         <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
         <v>10</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3871</v>
+        <v>3938</v>
       </c>
       <c r="C2" t="n">
-        <v>4050</v>
+        <v>2184</v>
       </c>
       <c r="D2" t="n">
-        <v>21756</v>
+        <v>21632</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4550</v>
+        <v>4573</v>
       </c>
       <c r="C3" t="n">
-        <v>9008</v>
+        <v>5321</v>
       </c>
       <c r="D3" t="n">
-        <v>16665</v>
+        <v>22443</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2346</v>
+        <v>2515</v>
       </c>
       <c r="C4" t="n">
-        <v>9792</v>
+        <v>7878</v>
       </c>
       <c r="D4" t="n">
-        <v>8710</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1279</v>
+        <v>1398</v>
       </c>
       <c r="C5" t="n">
-        <v>6653</v>
+        <v>5757</v>
       </c>
       <c r="D5" t="n">
-        <v>3200</v>
+        <v>3917</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>749</v>
+        <v>794</v>
       </c>
       <c r="C6" t="n">
-        <v>4026</v>
+        <v>3331</v>
       </c>
       <c r="D6" t="n">
-        <v>940</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="C7" t="n">
-        <v>2487</v>
+        <v>2052</v>
       </c>
       <c r="D7" t="n">
-        <v>506</v>
+        <v>527</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>1291</v>
+        <v>1066</v>
       </c>
       <c r="D8" t="n">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9">
@@ -2125,10 +2125,10 @@
         <v>40</v>
       </c>
       <c r="C9" t="n">
-        <v>464</v>
+        <v>419</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="D10" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2167,7 +2167,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
         <v>131</v>
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2195,7 +2195,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n">
         <v>59</v>
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2226,7 +2226,7 @@
         <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3760</v>
+        <v>4417</v>
       </c>
       <c r="C2" t="n">
-        <v>4413</v>
+        <v>8152</v>
       </c>
       <c r="D2" t="n">
-        <v>23940</v>
+        <v>21693</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3595</v>
+        <v>3621</v>
       </c>
       <c r="C3" t="n">
-        <v>5943</v>
+        <v>3394</v>
       </c>
       <c r="D3" t="n">
-        <v>16237</v>
+        <v>20824</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2789</v>
+        <v>2925</v>
       </c>
       <c r="C4" t="n">
-        <v>9212</v>
+        <v>6537</v>
       </c>
       <c r="D4" t="n">
-        <v>9743</v>
+        <v>13339</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1527</v>
+        <v>1653</v>
       </c>
       <c r="C5" t="n">
-        <v>8024</v>
+        <v>6614</v>
       </c>
       <c r="D5" t="n">
-        <v>3949</v>
+        <v>5039</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>891</v>
+        <v>950</v>
       </c>
       <c r="C6" t="n">
-        <v>5123</v>
+        <v>4402</v>
       </c>
       <c r="D6" t="n">
-        <v>1253</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="C7" t="n">
-        <v>3158</v>
+        <v>2590</v>
       </c>
       <c r="D7" t="n">
-        <v>560</v>
+        <v>592</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C8" t="n">
-        <v>1771</v>
+        <v>1472</v>
       </c>
       <c r="D8" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9">
@@ -2436,10 +2436,10 @@
         <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>768</v>
+        <v>667</v>
       </c>
       <c r="D9" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>314</v>
+        <v>293</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14">
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
         <v>61</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2537,7 @@
         <v>35</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D17" t="n">
         <v>23</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2286</v>
+        <v>2643</v>
       </c>
       <c r="C2" t="n">
-        <v>2178</v>
+        <v>3802</v>
       </c>
       <c r="D2" t="n">
-        <v>16708</v>
+        <v>15140</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3507</v>
+        <v>3673</v>
       </c>
       <c r="C3" t="n">
-        <v>5234</v>
+        <v>4889</v>
       </c>
       <c r="D3" t="n">
-        <v>16674</v>
+        <v>20447</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3054</v>
+        <v>3213</v>
       </c>
       <c r="C4" t="n">
-        <v>8957</v>
+        <v>6065</v>
       </c>
       <c r="D4" t="n">
-        <v>10513</v>
+        <v>14268</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1569</v>
+        <v>1698</v>
       </c>
       <c r="C5" t="n">
-        <v>9515</v>
+        <v>7608</v>
       </c>
       <c r="D5" t="n">
-        <v>4168</v>
+        <v>5328</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>721</v>
+        <v>766</v>
       </c>
       <c r="C6" t="n">
-        <v>6029</v>
+        <v>5210</v>
       </c>
       <c r="D6" t="n">
-        <v>1230</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C7" t="n">
-        <v>3257</v>
+        <v>2695</v>
       </c>
       <c r="D7" t="n">
-        <v>563</v>
+        <v>588</v>
       </c>
     </row>
     <row r="8">
@@ -2733,7 +2733,7 @@
         <v>46</v>
       </c>
       <c r="C8" t="n">
-        <v>1273</v>
+        <v>1100</v>
       </c>
       <c r="D8" t="n">
         <v>375</v>
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
         <v>59</v>
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2834,7 +2834,7 @@
         <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
         <v>22</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
         <v>5</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2780</v>
+        <v>3158</v>
       </c>
       <c r="C2" t="n">
-        <v>4161</v>
+        <v>7512</v>
       </c>
       <c r="D2" t="n">
-        <v>15622</v>
+        <v>13666</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2584</v>
+        <v>2775</v>
       </c>
       <c r="C3" t="n">
-        <v>3466</v>
+        <v>3914</v>
       </c>
       <c r="D3" t="n">
-        <v>15584</v>
+        <v>18547</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2852</v>
+        <v>2999</v>
       </c>
       <c r="C4" t="n">
-        <v>7141</v>
+        <v>5443</v>
       </c>
       <c r="D4" t="n">
-        <v>11139</v>
+        <v>14783</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1899</v>
+        <v>2040</v>
       </c>
       <c r="C5" t="n">
-        <v>9167</v>
+        <v>6841</v>
       </c>
       <c r="D5" t="n">
-        <v>4954</v>
+        <v>6453</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>927</v>
+        <v>1003</v>
       </c>
       <c r="C6" t="n">
-        <v>7440</v>
+        <v>6204</v>
       </c>
       <c r="D6" t="n">
-        <v>1620</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="C7" t="n">
-        <v>4347</v>
+        <v>3706</v>
       </c>
       <c r="D7" t="n">
-        <v>635</v>
+        <v>691</v>
       </c>
     </row>
     <row r="8">
@@ -3044,10 +3044,10 @@
         <v>60</v>
       </c>
       <c r="C8" t="n">
-        <v>2009</v>
+        <v>1710</v>
       </c>
       <c r="D8" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>606</v>
+        <v>547</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3145,7 +3145,7 @@
         <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1883</v>
+        <v>2108</v>
       </c>
       <c r="C2" t="n">
-        <v>2407</v>
+        <v>4304</v>
       </c>
       <c r="D2" t="n">
-        <v>12570</v>
+        <v>10104</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2319</v>
+        <v>2539</v>
       </c>
       <c r="C3" t="n">
-        <v>3394</v>
+        <v>4823</v>
       </c>
       <c r="D3" t="n">
-        <v>14765</v>
+        <v>16952</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2558</v>
+        <v>2702</v>
       </c>
       <c r="C4" t="n">
-        <v>5751</v>
+        <v>4870</v>
       </c>
       <c r="D4" t="n">
-        <v>11462</v>
+        <v>15123</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2054</v>
+        <v>2202</v>
       </c>
       <c r="C5" t="n">
-        <v>8628</v>
+        <v>6399</v>
       </c>
       <c r="D5" t="n">
-        <v>5551</v>
+        <v>7198</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1089</v>
+        <v>1192</v>
       </c>
       <c r="C6" t="n">
-        <v>8254</v>
+        <v>6722</v>
       </c>
       <c r="D6" t="n">
-        <v>1888</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="C7" t="n">
-        <v>5298</v>
+        <v>4509</v>
       </c>
       <c r="D7" t="n">
-        <v>707</v>
+        <v>775</v>
       </c>
     </row>
     <row r="8">
@@ -3355,7 +3355,7 @@
         <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>2584</v>
+        <v>2216</v>
       </c>
       <c r="D8" t="n">
         <v>410</v>
@@ -3369,10 +3369,10 @@
         <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>667</v>
+        <v>623</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
         <v>136</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2567</v>
+        <v>3416</v>
       </c>
       <c r="C2" t="n">
-        <v>8743</v>
+        <v>12732</v>
       </c>
       <c r="D2" t="n">
-        <v>14712</v>
+        <v>15502</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1826</v>
+        <v>2008</v>
       </c>
       <c r="C3" t="n">
-        <v>2685</v>
+        <v>4107</v>
       </c>
       <c r="D3" t="n">
-        <v>13698</v>
+        <v>15045</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2173</v>
+        <v>2321</v>
       </c>
       <c r="C4" t="n">
-        <v>4658</v>
+        <v>4748</v>
       </c>
       <c r="D4" t="n">
-        <v>11447</v>
+        <v>14926</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2025</v>
+        <v>2163</v>
       </c>
       <c r="C5" t="n">
-        <v>7316</v>
+        <v>5649</v>
       </c>
       <c r="D5" t="n">
-        <v>6176</v>
+        <v>8044</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1303</v>
+        <v>1423</v>
       </c>
       <c r="C6" t="n">
-        <v>8326</v>
+        <v>6541</v>
       </c>
       <c r="D6" t="n">
-        <v>2320</v>
+        <v>2913</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>440</v>
+        <v>483</v>
       </c>
       <c r="C7" t="n">
-        <v>6419</v>
+        <v>5331</v>
       </c>
       <c r="D7" t="n">
-        <v>838</v>
+        <v>950</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>3487</v>
+        <v>3045</v>
       </c>
       <c r="D8" t="n">
-        <v>437</v>
+        <v>445</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>1274</v>
+        <v>1144</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10">
@@ -3694,7 +3694,7 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="D10" t="n">
         <v>186</v>
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D11" t="n">
         <v>139</v>
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5086</v>
+        <v>4299</v>
       </c>
       <c r="C2" t="n">
-        <v>9767</v>
+        <v>8143</v>
       </c>
       <c r="D2" t="n">
-        <v>12072</v>
+        <v>10550</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1856</v>
+        <v>2442</v>
       </c>
       <c r="C2" t="n">
-        <v>5105</v>
+        <v>7334</v>
       </c>
       <c r="D2" t="n">
-        <v>10945</v>
+        <v>11409</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2483</v>
+        <v>2762</v>
       </c>
       <c r="C3" t="n">
-        <v>4234</v>
+        <v>6400</v>
       </c>
       <c r="D3" t="n">
-        <v>14743</v>
+        <v>16438</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2963</v>
+        <v>3184</v>
       </c>
       <c r="C4" t="n">
-        <v>7091</v>
+        <v>6741</v>
       </c>
       <c r="D4" t="n">
-        <v>11702</v>
+        <v>15256</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1241</v>
+        <v>1354</v>
       </c>
       <c r="C5" t="n">
-        <v>11244</v>
+        <v>8761</v>
       </c>
       <c r="D5" t="n">
-        <v>5606</v>
+        <v>7219</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>406</v>
+        <v>446</v>
       </c>
       <c r="C6" t="n">
-        <v>7840</v>
+        <v>6506</v>
       </c>
       <c r="D6" t="n">
-        <v>1828</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C7" t="n">
-        <v>3417</v>
+        <v>2984</v>
       </c>
       <c r="D7" t="n">
-        <v>535</v>
+        <v>557</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>1248</v>
+        <v>1121</v>
       </c>
       <c r="D8" t="n">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9">
@@ -4302,7 +4302,7 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="D9" t="n">
         <v>182</v>
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D10" t="n">
         <v>136</v>
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D11" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6433</v>
+        <v>5929</v>
       </c>
       <c r="C2" t="n">
-        <v>8500</v>
+        <v>5351</v>
       </c>
       <c r="D2" t="n">
-        <v>12782</v>
+        <v>24482</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2162</v>
+        <v>1828</v>
       </c>
       <c r="C3" t="n">
-        <v>4922</v>
+        <v>4104</v>
       </c>
       <c r="D3" t="n">
-        <v>2667</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="4">
@@ -4554,7 +4554,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
         <v>381</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4712</v>
+        <v>4567</v>
       </c>
       <c r="C2" t="n">
-        <v>6612</v>
+        <v>5461</v>
       </c>
       <c r="D2" t="n">
-        <v>18455</v>
+        <v>25662</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3527</v>
+        <v>3182</v>
       </c>
       <c r="C3" t="n">
-        <v>5990</v>
+        <v>4147</v>
       </c>
       <c r="D3" t="n">
-        <v>4170</v>
+        <v>5941</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>973</v>
+        <v>828</v>
       </c>
       <c r="C4" t="n">
-        <v>2928</v>
+        <v>2449</v>
       </c>
       <c r="D4" t="n">
-        <v>1718</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="5">
@@ -4865,7 +4865,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C5" t="n">
         <v>219</v>
@@ -4885,7 +4885,7 @@
         <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>853</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4030</v>
+        <v>4927</v>
       </c>
       <c r="C2" t="n">
-        <v>5607</v>
+        <v>8115</v>
       </c>
       <c r="D2" t="n">
-        <v>30566</v>
+        <v>21961</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3379</v>
+        <v>3172</v>
       </c>
       <c r="C3" t="n">
-        <v>5478</v>
+        <v>4209</v>
       </c>
       <c r="D3" t="n">
-        <v>6155</v>
+        <v>8668</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1911</v>
+        <v>1702</v>
       </c>
       <c r="C4" t="n">
-        <v>4601</v>
+        <v>3359</v>
       </c>
       <c r="D4" t="n">
-        <v>2136</v>
+        <v>2436</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>451</v>
+        <v>393</v>
       </c>
       <c r="C5" t="n">
-        <v>1696</v>
+        <v>1434</v>
       </c>
       <c r="D5" t="n">
-        <v>1244</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="6">
@@ -5196,7 +5196,7 @@
         <v>304</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>903</v>
       </c>
     </row>
     <row r="7">
@@ -5210,7 +5210,7 @@
         <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>629</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5373</v>
+        <v>6586</v>
       </c>
       <c r="C2" t="n">
-        <v>12110</v>
+        <v>4976</v>
       </c>
       <c r="D2" t="n">
-        <v>27641</v>
+        <v>28358</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3037</v>
+        <v>3284</v>
       </c>
       <c r="C3" t="n">
-        <v>4878</v>
+        <v>5413</v>
       </c>
       <c r="D3" t="n">
-        <v>9432</v>
+        <v>10078</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2219</v>
+        <v>2067</v>
       </c>
       <c r="C4" t="n">
-        <v>4924</v>
+        <v>3746</v>
       </c>
       <c r="D4" t="n">
-        <v>2804</v>
+        <v>3498</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>970</v>
+        <v>855</v>
       </c>
       <c r="C5" t="n">
-        <v>3166</v>
+        <v>2388</v>
       </c>
       <c r="D5" t="n">
-        <v>1348</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>258</v>
+        <v>239</v>
       </c>
       <c r="C6" t="n">
-        <v>992</v>
+        <v>875</v>
       </c>
       <c r="D6" t="n">
-        <v>953</v>
+        <v>947</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
         <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
@@ -5563,7 +5563,7 @@
         <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5574,7 +5574,7 @@
         <v>49</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5588,7 +5588,7 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
         <v>217</v>
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5975</v>
+        <v>6902</v>
       </c>
       <c r="C2" t="n">
-        <v>9949</v>
+        <v>11979</v>
       </c>
       <c r="D2" t="n">
-        <v>24434</v>
+        <v>39458</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3047</v>
+        <v>3540</v>
       </c>
       <c r="C3" t="n">
-        <v>6969</v>
+        <v>4251</v>
       </c>
       <c r="D3" t="n">
-        <v>10852</v>
+        <v>11428</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1613</v>
+        <v>1649</v>
       </c>
       <c r="C4" t="n">
-        <v>3970</v>
+        <v>3821</v>
       </c>
       <c r="D4" t="n">
-        <v>3428</v>
+        <v>4006</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>823</v>
+        <v>762</v>
       </c>
       <c r="C5" t="n">
-        <v>2976</v>
+        <v>2240</v>
       </c>
       <c r="D5" t="n">
-        <v>1252</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>289</v>
+        <v>257</v>
       </c>
       <c r="C6" t="n">
-        <v>1384</v>
+        <v>1103</v>
       </c>
       <c r="D6" t="n">
-        <v>776</v>
+        <v>778</v>
       </c>
     </row>
     <row r="7">
@@ -5826,10 +5826,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C7" t="n">
-        <v>425</v>
+        <v>389</v>
       </c>
       <c r="D7" t="n">
         <v>514</v>
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
         <v>117</v>
@@ -5941,10 +5941,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4848</v>
+        <v>5409</v>
       </c>
       <c r="C2" t="n">
-        <v>9168</v>
+        <v>7303</v>
       </c>
       <c r="D2" t="n">
-        <v>17513</v>
+        <v>35045</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3731</v>
+        <v>4318</v>
       </c>
       <c r="C3" t="n">
-        <v>7556</v>
+        <v>7547</v>
       </c>
       <c r="D3" t="n">
-        <v>12335</v>
+        <v>15295</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2037</v>
+        <v>2256</v>
       </c>
       <c r="C4" t="n">
-        <v>5634</v>
+        <v>4001</v>
       </c>
       <c r="D4" t="n">
-        <v>4820</v>
+        <v>5342</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="C5" t="n">
-        <v>3496</v>
+        <v>3119</v>
       </c>
       <c r="D5" t="n">
-        <v>1619</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>514</v>
+        <v>470</v>
       </c>
       <c r="C6" t="n">
-        <v>2268</v>
+        <v>1733</v>
       </c>
       <c r="D6" t="n">
-        <v>856</v>
+        <v>881</v>
       </c>
     </row>
     <row r="7">
@@ -6137,10 +6137,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="C7" t="n">
-        <v>960</v>
+        <v>787</v>
       </c>
       <c r="D7" t="n">
         <v>552</v>
@@ -6154,7 +6154,7 @@
         <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>332</v>
+        <v>311</v>
       </c>
       <c r="D8" t="n">
         <v>385</v>
@@ -6168,10 +6168,10 @@
         <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
         <v>153</v>
@@ -6238,7 +6238,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6255,7 +6255,7 @@
         <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6294,10 +6294,10 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5342</v>
+        <v>4389</v>
       </c>
       <c r="C2" t="n">
-        <v>7249</v>
+        <v>6632</v>
       </c>
       <c r="D2" t="n">
-        <v>18123</v>
+        <v>38952</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3514</v>
+        <v>4033</v>
       </c>
       <c r="C3" t="n">
-        <v>7300</v>
+        <v>6431</v>
       </c>
       <c r="D3" t="n">
-        <v>12275</v>
+        <v>17353</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2445</v>
+        <v>2784</v>
       </c>
       <c r="C4" t="n">
-        <v>6586</v>
+        <v>5892</v>
       </c>
       <c r="D4" t="n">
-        <v>6116</v>
+        <v>7090</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1361</v>
+        <v>1449</v>
       </c>
       <c r="C5" t="n">
-        <v>4572</v>
+        <v>3498</v>
       </c>
       <c r="D5" t="n">
-        <v>2153</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>712</v>
+        <v>690</v>
       </c>
       <c r="C6" t="n">
-        <v>2856</v>
+        <v>2445</v>
       </c>
       <c r="D6" t="n">
-        <v>967</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>299</v>
+        <v>273</v>
       </c>
       <c r="C7" t="n">
-        <v>1638</v>
+        <v>1278</v>
       </c>
       <c r="D7" t="n">
-        <v>599</v>
+        <v>604</v>
       </c>
     </row>
     <row r="8">
@@ -6462,10 +6462,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>645</v>
+        <v>548</v>
       </c>
       <c r="D8" t="n">
         <v>405</v>
@@ -6479,10 +6479,10 @@
         <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6535,7 +6535,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
         <v>121</v>
@@ -6566,7 +6566,7 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6577,7 +6577,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
         <v>63</v>
@@ -6591,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
         <v>28</v>

--- a/output/yearly_population_iteration_31_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_31_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5609</v>
+        <v>4718</v>
       </c>
       <c r="C2" t="n">
-        <v>6252</v>
+        <v>6878</v>
       </c>
       <c r="D2" t="n">
-        <v>37384</v>
+        <v>21284</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3504</v>
+        <v>3229</v>
       </c>
       <c r="C3" t="n">
-        <v>5713</v>
+        <v>8149</v>
       </c>
       <c r="D3" t="n">
-        <v>19269</v>
+        <v>14090</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2863</v>
+        <v>2412</v>
       </c>
       <c r="C4" t="n">
-        <v>5987</v>
+        <v>5942</v>
       </c>
       <c r="D4" t="n">
-        <v>8579</v>
+        <v>6115</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1796</v>
+        <v>1592</v>
       </c>
       <c r="C5" t="n">
-        <v>4620</v>
+        <v>4657</v>
       </c>
       <c r="D5" t="n">
-        <v>3156</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>944</v>
+        <v>960</v>
       </c>
       <c r="C6" t="n">
-        <v>2901</v>
+        <v>3990</v>
       </c>
       <c r="D6" t="n">
-        <v>1258</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>408</v>
+        <v>459</v>
       </c>
       <c r="C7" t="n">
-        <v>1837</v>
+        <v>2833</v>
       </c>
       <c r="D7" t="n">
-        <v>661</v>
+        <v>634</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>884</v>
+        <v>1347</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C9" t="n">
-        <v>381</v>
+        <v>506</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -892,10 +892,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="D10" t="n">
         <v>244</v>
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
         <v>203</v>
@@ -926,7 +926,7 @@
         <v>127</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -954,7 +954,7 @@
         <v>76</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -965,7 +965,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5735</v>
+        <v>6178</v>
       </c>
       <c r="C2" t="n">
-        <v>5859</v>
+        <v>12263</v>
       </c>
       <c r="D2" t="n">
-        <v>35539</v>
+        <v>16860</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3601</v>
+        <v>3160</v>
       </c>
       <c r="C3" t="n">
-        <v>5247</v>
+        <v>6709</v>
       </c>
       <c r="D3" t="n">
-        <v>20437</v>
+        <v>14086</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2711</v>
+        <v>2374</v>
       </c>
       <c r="C4" t="n">
-        <v>5733</v>
+        <v>6835</v>
       </c>
       <c r="D4" t="n">
-        <v>10062</v>
+        <v>7095</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1980</v>
+        <v>1707</v>
       </c>
       <c r="C5" t="n">
-        <v>5096</v>
+        <v>5082</v>
       </c>
       <c r="D5" t="n">
-        <v>3862</v>
+        <v>2736</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1180</v>
+        <v>1111</v>
       </c>
       <c r="C6" t="n">
-        <v>3632</v>
+        <v>4240</v>
       </c>
       <c r="D6" t="n">
-        <v>1532</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>567</v>
+        <v>595</v>
       </c>
       <c r="C7" t="n">
-        <v>2277</v>
+        <v>3291</v>
       </c>
       <c r="D7" t="n">
-        <v>735</v>
+        <v>685</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>225</v>
+        <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>1285</v>
+        <v>1944</v>
       </c>
       <c r="D8" t="n">
-        <v>461</v>
+        <v>446</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C9" t="n">
-        <v>579</v>
+        <v>843</v>
       </c>
       <c r="D9" t="n">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C10" t="n">
-        <v>279</v>
+        <v>333</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1265,7 +1265,7 @@
         <v>82</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6936</v>
+        <v>8238</v>
       </c>
       <c r="C2" t="n">
-        <v>5581</v>
+        <v>17924</v>
       </c>
       <c r="D2" t="n">
-        <v>36098</v>
+        <v>20012</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3630</v>
+        <v>3502</v>
       </c>
       <c r="C3" t="n">
-        <v>4883</v>
+        <v>7889</v>
       </c>
       <c r="D3" t="n">
-        <v>20941</v>
+        <v>13517</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2613</v>
+        <v>2283</v>
       </c>
       <c r="C4" t="n">
-        <v>5353</v>
+        <v>6575</v>
       </c>
       <c r="D4" t="n">
-        <v>11153</v>
+        <v>7886</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2020</v>
+        <v>1748</v>
       </c>
       <c r="C5" t="n">
-        <v>5204</v>
+        <v>5634</v>
       </c>
       <c r="D5" t="n">
-        <v>4637</v>
+        <v>3212</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1370</v>
+        <v>1224</v>
       </c>
       <c r="C6" t="n">
-        <v>4190</v>
+        <v>4534</v>
       </c>
       <c r="D6" t="n">
-        <v>1810</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="C7" t="n">
-        <v>2784</v>
+        <v>3620</v>
       </c>
       <c r="D7" t="n">
-        <v>836</v>
+        <v>733</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>311</v>
+        <v>340</v>
       </c>
       <c r="C8" t="n">
-        <v>1651</v>
+        <v>2425</v>
       </c>
       <c r="D8" t="n">
-        <v>486</v>
+        <v>467</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="C9" t="n">
-        <v>841</v>
+        <v>1233</v>
       </c>
       <c r="D9" t="n">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>381</v>
+        <v>512</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1562,7 +1562,7 @@
         <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6360</v>
+        <v>7403</v>
       </c>
       <c r="C2" t="n">
-        <v>3839</v>
+        <v>12475</v>
       </c>
       <c r="D2" t="n">
-        <v>29883</v>
+        <v>16658</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4514</v>
+        <v>4123</v>
       </c>
       <c r="C3" t="n">
-        <v>7522</v>
+        <v>12277</v>
       </c>
       <c r="D3" t="n">
-        <v>22524</v>
+        <v>14750</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1866</v>
+        <v>1615</v>
       </c>
       <c r="C4" t="n">
-        <v>7925</v>
+        <v>8880</v>
       </c>
       <c r="D4" t="n">
-        <v>10485</v>
+        <v>7368</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1265</v>
+        <v>1130</v>
       </c>
       <c r="C5" t="n">
-        <v>4106</v>
+        <v>4443</v>
       </c>
       <c r="D5" t="n">
-        <v>3020</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="C6" t="n">
-        <v>2728</v>
+        <v>3547</v>
       </c>
       <c r="D6" t="n">
-        <v>819</v>
+        <v>718</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>287</v>
+        <v>314</v>
       </c>
       <c r="C7" t="n">
-        <v>1617</v>
+        <v>2376</v>
       </c>
       <c r="D7" t="n">
-        <v>476</v>
+        <v>457</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C8" t="n">
-        <v>824</v>
+        <v>1208</v>
       </c>
       <c r="D8" t="n">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>373</v>
+        <v>501</v>
       </c>
       <c r="D9" t="n">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>229</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12">
@@ -1859,7 +1859,7 @@
         <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
         <v>49</v>
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
         <v>10</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3938</v>
+        <v>4295</v>
       </c>
       <c r="C2" t="n">
-        <v>2184</v>
+        <v>5709</v>
       </c>
       <c r="D2" t="n">
-        <v>21632</v>
+        <v>11726</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4573</v>
+        <v>4663</v>
       </c>
       <c r="C3" t="n">
-        <v>5321</v>
+        <v>11236</v>
       </c>
       <c r="D3" t="n">
-        <v>22443</v>
+        <v>14168</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2515</v>
+        <v>2204</v>
       </c>
       <c r="C4" t="n">
-        <v>7878</v>
+        <v>10569</v>
       </c>
       <c r="D4" t="n">
-        <v>12000</v>
+        <v>8348</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1398</v>
+        <v>1249</v>
       </c>
       <c r="C5" t="n">
-        <v>5757</v>
+        <v>6310</v>
       </c>
       <c r="D5" t="n">
-        <v>3917</v>
+        <v>2775</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>794</v>
+        <v>770</v>
       </c>
       <c r="C6" t="n">
-        <v>3331</v>
+        <v>4022</v>
       </c>
       <c r="D6" t="n">
-        <v>1044</v>
+        <v>858</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>267</v>
+        <v>291</v>
       </c>
       <c r="C7" t="n">
-        <v>2052</v>
+        <v>2882</v>
       </c>
       <c r="D7" t="n">
-        <v>527</v>
+        <v>495</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="C8" t="n">
-        <v>1066</v>
+        <v>1553</v>
       </c>
       <c r="D8" t="n">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C9" t="n">
-        <v>419</v>
+        <v>537</v>
       </c>
       <c r="D9" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
+        <v>164</v>
+      </c>
+      <c r="D11" t="n">
         <v>165</v>
-      </c>
-      <c r="D11" t="n">
-        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4417</v>
+        <v>3862</v>
       </c>
       <c r="C2" t="n">
-        <v>8152</v>
+        <v>10389</v>
       </c>
       <c r="D2" t="n">
-        <v>21693</v>
+        <v>15773</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3621</v>
+        <v>3792</v>
       </c>
       <c r="C3" t="n">
-        <v>3394</v>
+        <v>7784</v>
       </c>
       <c r="D3" t="n">
-        <v>20824</v>
+        <v>12883</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2925</v>
+        <v>2772</v>
       </c>
       <c r="C4" t="n">
-        <v>6537</v>
+        <v>10662</v>
       </c>
       <c r="D4" t="n">
-        <v>13339</v>
+        <v>9044</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1653</v>
+        <v>1456</v>
       </c>
       <c r="C5" t="n">
-        <v>6614</v>
+        <v>8100</v>
       </c>
       <c r="D5" t="n">
-        <v>5039</v>
+        <v>3546</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>950</v>
+        <v>883</v>
       </c>
       <c r="C6" t="n">
-        <v>4402</v>
+        <v>5012</v>
       </c>
       <c r="D6" t="n">
-        <v>1443</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="C7" t="n">
-        <v>2590</v>
+        <v>3350</v>
       </c>
       <c r="D7" t="n">
-        <v>592</v>
+        <v>539</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="C8" t="n">
-        <v>1472</v>
+        <v>2088</v>
       </c>
       <c r="D8" t="n">
-        <v>355</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>667</v>
+        <v>915</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>293</v>
+        <v>336</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
         <v>133</v>
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D13" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
         <v>35</v>
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2643</v>
+        <v>2338</v>
       </c>
       <c r="C2" t="n">
-        <v>3802</v>
+        <v>5008</v>
       </c>
       <c r="D2" t="n">
-        <v>15140</v>
+        <v>11001</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3673</v>
+        <v>3677</v>
       </c>
       <c r="C3" t="n">
-        <v>4889</v>
+        <v>8405</v>
       </c>
       <c r="D3" t="n">
-        <v>20447</v>
+        <v>12894</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3213</v>
+        <v>3045</v>
       </c>
       <c r="C4" t="n">
-        <v>6065</v>
+        <v>10579</v>
       </c>
       <c r="D4" t="n">
-        <v>14268</v>
+        <v>9602</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1698</v>
+        <v>1522</v>
       </c>
       <c r="C5" t="n">
-        <v>7608</v>
+        <v>9982</v>
       </c>
       <c r="D5" t="n">
-        <v>5328</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>766</v>
+        <v>727</v>
       </c>
       <c r="C6" t="n">
-        <v>5210</v>
+        <v>5868</v>
       </c>
       <c r="D6" t="n">
-        <v>1403</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="C7" t="n">
-        <v>2695</v>
+        <v>3619</v>
       </c>
       <c r="D7" t="n">
-        <v>588</v>
+        <v>547</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C8" t="n">
-        <v>1100</v>
+        <v>1490</v>
       </c>
       <c r="D8" t="n">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>287</v>
+        <v>329</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D11" t="n">
         <v>130</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2806,7 +2806,7 @@
         <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
         <v>34</v>
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D18" t="n">
         <v>5</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3158</v>
+        <v>2463</v>
       </c>
       <c r="C2" t="n">
-        <v>7512</v>
+        <v>8080</v>
       </c>
       <c r="D2" t="n">
-        <v>13666</v>
+        <v>10866</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2775</v>
+        <v>2703</v>
       </c>
       <c r="C3" t="n">
-        <v>3914</v>
+        <v>6199</v>
       </c>
       <c r="D3" t="n">
-        <v>18547</v>
+        <v>11805</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2999</v>
+        <v>2871</v>
       </c>
       <c r="C4" t="n">
-        <v>5443</v>
+        <v>9378</v>
       </c>
       <c r="D4" t="n">
-        <v>14783</v>
+        <v>9815</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2040</v>
+        <v>1866</v>
       </c>
       <c r="C5" t="n">
-        <v>6841</v>
+        <v>10128</v>
       </c>
       <c r="D5" t="n">
-        <v>6453</v>
+        <v>4460</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1003</v>
+        <v>925</v>
       </c>
       <c r="C6" t="n">
-        <v>6204</v>
+        <v>7532</v>
       </c>
       <c r="D6" t="n">
-        <v>1912</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="C7" t="n">
-        <v>3706</v>
+        <v>4548</v>
       </c>
       <c r="D7" t="n">
-        <v>691</v>
+        <v>606</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C8" t="n">
-        <v>1710</v>
+        <v>2248</v>
       </c>
       <c r="D8" t="n">
-        <v>397</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>547</v>
+        <v>691</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
         <v>32</v>
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2108</v>
+        <v>1676</v>
       </c>
       <c r="C2" t="n">
-        <v>4304</v>
+        <v>4207</v>
       </c>
       <c r="D2" t="n">
-        <v>10104</v>
+        <v>7737</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2539</v>
+        <v>2308</v>
       </c>
       <c r="C3" t="n">
-        <v>4823</v>
+        <v>6285</v>
       </c>
       <c r="D3" t="n">
-        <v>16952</v>
+        <v>11076</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2702</v>
+        <v>2601</v>
       </c>
       <c r="C4" t="n">
-        <v>4870</v>
+        <v>8232</v>
       </c>
       <c r="D4" t="n">
-        <v>15123</v>
+        <v>9859</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2202</v>
+        <v>2023</v>
       </c>
       <c r="C5" t="n">
-        <v>6399</v>
+        <v>9957</v>
       </c>
       <c r="D5" t="n">
-        <v>7198</v>
+        <v>4975</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1192</v>
+        <v>1068</v>
       </c>
       <c r="C6" t="n">
-        <v>6722</v>
+        <v>8600</v>
       </c>
       <c r="D6" t="n">
-        <v>2337</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="C7" t="n">
-        <v>4509</v>
+        <v>5530</v>
       </c>
       <c r="D7" t="n">
-        <v>775</v>
+        <v>670</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>2216</v>
+        <v>2808</v>
       </c>
       <c r="D8" t="n">
-        <v>410</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>623</v>
+        <v>749</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
         <v>35</v>
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3416</v>
+        <v>2231</v>
       </c>
       <c r="C2" t="n">
-        <v>12732</v>
+        <v>9987</v>
       </c>
       <c r="D2" t="n">
-        <v>15502</v>
+        <v>15302</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2008</v>
+        <v>1767</v>
       </c>
       <c r="C3" t="n">
-        <v>4107</v>
+        <v>4913</v>
       </c>
       <c r="D3" t="n">
-        <v>15045</v>
+        <v>10010</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2321</v>
+        <v>2197</v>
       </c>
       <c r="C4" t="n">
-        <v>4748</v>
+        <v>7275</v>
       </c>
       <c r="D4" t="n">
-        <v>14926</v>
+        <v>9722</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2163</v>
+        <v>2014</v>
       </c>
       <c r="C5" t="n">
-        <v>5649</v>
+        <v>9087</v>
       </c>
       <c r="D5" t="n">
-        <v>8044</v>
+        <v>5385</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1423</v>
+        <v>1272</v>
       </c>
       <c r="C6" t="n">
-        <v>6541</v>
+        <v>9026</v>
       </c>
       <c r="D6" t="n">
-        <v>2913</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>483</v>
+        <v>425</v>
       </c>
       <c r="C7" t="n">
-        <v>5331</v>
+        <v>6665</v>
       </c>
       <c r="D7" t="n">
-        <v>950</v>
+        <v>783</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C8" t="n">
-        <v>3045</v>
+        <v>3687</v>
       </c>
       <c r="D8" t="n">
-        <v>445</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>1144</v>
+        <v>1381</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>342</v>
+        <v>372</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3739,7 +3739,7 @@
         <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4299</v>
+        <v>5636</v>
       </c>
       <c r="C2" t="n">
-        <v>8143</v>
+        <v>14138</v>
       </c>
       <c r="D2" t="n">
-        <v>10550</v>
+        <v>7252</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2442</v>
+        <v>1649</v>
       </c>
       <c r="C2" t="n">
-        <v>7334</v>
+        <v>5913</v>
       </c>
       <c r="D2" t="n">
-        <v>11409</v>
+        <v>11384</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2762</v>
+        <v>2397</v>
       </c>
       <c r="C3" t="n">
-        <v>6400</v>
+        <v>6556</v>
       </c>
       <c r="D3" t="n">
-        <v>16438</v>
+        <v>11213</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3184</v>
+        <v>2984</v>
       </c>
       <c r="C4" t="n">
-        <v>6741</v>
+        <v>10274</v>
       </c>
       <c r="D4" t="n">
-        <v>15256</v>
+        <v>9930</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1354</v>
+        <v>1175</v>
       </c>
       <c r="C5" t="n">
-        <v>8761</v>
+        <v>13012</v>
       </c>
       <c r="D5" t="n">
-        <v>7219</v>
+        <v>4864</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>446</v>
+        <v>392</v>
       </c>
       <c r="C6" t="n">
-        <v>6506</v>
+        <v>8035</v>
       </c>
       <c r="D6" t="n">
-        <v>2237</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C7" t="n">
-        <v>2984</v>
+        <v>3613</v>
       </c>
       <c r="D7" t="n">
-        <v>557</v>
+        <v>511</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
-        <v>1121</v>
+        <v>1353</v>
       </c>
       <c r="D8" t="n">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>335</v>
+        <v>364</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D10" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5929</v>
+        <v>7286</v>
       </c>
       <c r="C2" t="n">
-        <v>5351</v>
+        <v>9163</v>
       </c>
       <c r="D2" t="n">
-        <v>24482</v>
+        <v>12195</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1828</v>
+        <v>2395</v>
       </c>
       <c r="C3" t="n">
-        <v>4104</v>
+        <v>7125</v>
       </c>
       <c r="D3" t="n">
-        <v>2411</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="4">
@@ -4554,7 +4554,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
         <v>381</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4567</v>
+        <v>4892</v>
       </c>
       <c r="C2" t="n">
-        <v>5461</v>
+        <v>9527</v>
       </c>
       <c r="D2" t="n">
-        <v>25662</v>
+        <v>15309</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3182</v>
+        <v>3972</v>
       </c>
       <c r="C3" t="n">
-        <v>4147</v>
+        <v>7139</v>
       </c>
       <c r="D3" t="n">
-        <v>5941</v>
+        <v>3457</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>828</v>
+        <v>1075</v>
       </c>
       <c r="C4" t="n">
-        <v>2449</v>
+        <v>4218</v>
       </c>
       <c r="D4" t="n">
-        <v>1667</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="D6" t="n">
-        <v>853</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4927</v>
+        <v>4034</v>
       </c>
       <c r="C2" t="n">
-        <v>8115</v>
+        <v>7250</v>
       </c>
       <c r="D2" t="n">
-        <v>21961</v>
+        <v>17003</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3172</v>
+        <v>3677</v>
       </c>
       <c r="C3" t="n">
-        <v>4209</v>
+        <v>7298</v>
       </c>
       <c r="D3" t="n">
-        <v>8668</v>
+        <v>5104</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1702</v>
+        <v>2109</v>
       </c>
       <c r="C4" t="n">
-        <v>3359</v>
+        <v>5756</v>
       </c>
       <c r="D4" t="n">
-        <v>2436</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>393</v>
+        <v>493</v>
       </c>
       <c r="C5" t="n">
-        <v>1434</v>
+        <v>2363</v>
       </c>
       <c r="D5" t="n">
-        <v>1235</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
         <v>304</v>
       </c>
       <c r="D6" t="n">
-        <v>903</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D7" t="n">
-        <v>629</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6586</v>
+        <v>4775</v>
       </c>
       <c r="C2" t="n">
-        <v>4976</v>
+        <v>4571</v>
       </c>
       <c r="D2" t="n">
-        <v>28358</v>
+        <v>25187</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3284</v>
+        <v>3176</v>
       </c>
       <c r="C3" t="n">
-        <v>5413</v>
+        <v>6342</v>
       </c>
       <c r="D3" t="n">
-        <v>10078</v>
+        <v>6553</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2067</v>
+        <v>2447</v>
       </c>
       <c r="C4" t="n">
-        <v>3746</v>
+        <v>6450</v>
       </c>
       <c r="D4" t="n">
-        <v>3498</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>855</v>
+        <v>1050</v>
       </c>
       <c r="C5" t="n">
-        <v>2388</v>
+        <v>4017</v>
       </c>
       <c r="D5" t="n">
-        <v>1393</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>239</v>
+        <v>276</v>
       </c>
       <c r="C6" t="n">
-        <v>875</v>
+        <v>1328</v>
       </c>
       <c r="D6" t="n">
-        <v>947</v>
+        <v>948</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D7" t="n">
-        <v>662</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D8" t="n">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D9" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5585,7 +5585,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
         <v>158</v>
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
         <v>122</v>
@@ -5644,7 +5644,7 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>100</v>
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6902</v>
+        <v>5591</v>
       </c>
       <c r="C2" t="n">
-        <v>11979</v>
+        <v>7810</v>
       </c>
       <c r="D2" t="n">
-        <v>39458</v>
+        <v>27263</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3540</v>
+        <v>2858</v>
       </c>
       <c r="C3" t="n">
-        <v>4251</v>
+        <v>4526</v>
       </c>
       <c r="D3" t="n">
-        <v>11428</v>
+        <v>8253</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1649</v>
+        <v>1727</v>
       </c>
       <c r="C4" t="n">
-        <v>3821</v>
+        <v>5174</v>
       </c>
       <c r="D4" t="n">
-        <v>4006</v>
+        <v>2634</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>762</v>
+        <v>906</v>
       </c>
       <c r="C5" t="n">
-        <v>2240</v>
+        <v>3832</v>
       </c>
       <c r="D5" t="n">
-        <v>1377</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>257</v>
+        <v>306</v>
       </c>
       <c r="C6" t="n">
-        <v>1103</v>
+        <v>1761</v>
       </c>
       <c r="D6" t="n">
-        <v>778</v>
+        <v>754</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C7" t="n">
-        <v>389</v>
+        <v>524</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
         <v>221</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D9" t="n">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
         <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
         <v>117</v>
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>96</v>
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5969,10 +5969,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5409</v>
+        <v>4664</v>
       </c>
       <c r="C2" t="n">
-        <v>7303</v>
+        <v>10685</v>
       </c>
       <c r="D2" t="n">
-        <v>35045</v>
+        <v>30453</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4318</v>
+        <v>3494</v>
       </c>
       <c r="C3" t="n">
-        <v>7547</v>
+        <v>5524</v>
       </c>
       <c r="D3" t="n">
-        <v>15295</v>
+        <v>10839</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2256</v>
+        <v>2001</v>
       </c>
       <c r="C4" t="n">
-        <v>4001</v>
+        <v>4680</v>
       </c>
       <c r="D4" t="n">
-        <v>5342</v>
+        <v>3686</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1075</v>
+        <v>1171</v>
       </c>
       <c r="C5" t="n">
-        <v>3119</v>
+        <v>4525</v>
       </c>
       <c r="D5" t="n">
-        <v>1865</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>470</v>
+        <v>551</v>
       </c>
       <c r="C6" t="n">
-        <v>1733</v>
+        <v>2893</v>
       </c>
       <c r="D6" t="n">
-        <v>881</v>
+        <v>821</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="C7" t="n">
-        <v>787</v>
+        <v>1197</v>
       </c>
       <c r="D7" t="n">
-        <v>552</v>
+        <v>559</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>311</v>
+        <v>384</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D9" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6238,7 +6238,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4389</v>
+        <v>4649</v>
       </c>
       <c r="C2" t="n">
-        <v>6632</v>
+        <v>11667</v>
       </c>
       <c r="D2" t="n">
-        <v>38952</v>
+        <v>26475</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4033</v>
+        <v>3338</v>
       </c>
       <c r="C3" t="n">
-        <v>6431</v>
+        <v>7152</v>
       </c>
       <c r="D3" t="n">
-        <v>17353</v>
+        <v>13057</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2784</v>
+        <v>2349</v>
       </c>
       <c r="C4" t="n">
-        <v>5892</v>
+        <v>5044</v>
       </c>
       <c r="D4" t="n">
-        <v>7090</v>
+        <v>4843</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1449</v>
+        <v>1379</v>
       </c>
       <c r="C5" t="n">
-        <v>3498</v>
+        <v>4469</v>
       </c>
       <c r="D5" t="n">
-        <v>2424</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>690</v>
+        <v>777</v>
       </c>
       <c r="C6" t="n">
-        <v>2445</v>
+        <v>3706</v>
       </c>
       <c r="D6" t="n">
-        <v>1048</v>
+        <v>901</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>273</v>
+        <v>314</v>
       </c>
       <c r="C7" t="n">
-        <v>1278</v>
+        <v>2060</v>
       </c>
       <c r="D7" t="n">
-        <v>604</v>
+        <v>599</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
-        <v>548</v>
+        <v>778</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>255</v>
+        <v>292</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -6490,10 +6490,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
         <v>239</v>
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
         <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
         <v>81</v>
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>

--- a/output/yearly_population_iteration_31_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_31_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4718</v>
+        <v>1253</v>
       </c>
       <c r="C2" t="n">
-        <v>6878</v>
+        <v>2400</v>
       </c>
       <c r="D2" t="n">
-        <v>21284</v>
+        <v>12913</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3229</v>
+        <v>2033</v>
       </c>
       <c r="C3" t="n">
-        <v>8149</v>
+        <v>6588</v>
       </c>
       <c r="D3" t="n">
-        <v>14090</v>
+        <v>13858</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2412</v>
+        <v>1312</v>
       </c>
       <c r="C4" t="n">
-        <v>5942</v>
+        <v>9006</v>
       </c>
       <c r="D4" t="n">
-        <v>6115</v>
+        <v>6448</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1592</v>
+        <v>634</v>
       </c>
       <c r="C5" t="n">
-        <v>4657</v>
+        <v>5758</v>
       </c>
       <c r="D5" t="n">
-        <v>2202</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>960</v>
+        <v>258</v>
       </c>
       <c r="C6" t="n">
-        <v>3990</v>
+        <v>2221</v>
       </c>
       <c r="D6" t="n">
-        <v>1030</v>
+        <v>738</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>459</v>
+        <v>98</v>
       </c>
       <c r="C7" t="n">
-        <v>2833</v>
+        <v>725</v>
       </c>
       <c r="D7" t="n">
-        <v>634</v>
+        <v>482</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>171</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>1347</v>
+        <v>345</v>
       </c>
       <c r="D8" t="n">
-        <v>427</v>
+        <v>372</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>506</v>
+        <v>281</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>141</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6178</v>
+        <v>1017</v>
       </c>
       <c r="C2" t="n">
-        <v>12263</v>
+        <v>4901</v>
       </c>
       <c r="D2" t="n">
-        <v>16860</v>
+        <v>12549</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3160</v>
+        <v>1406</v>
       </c>
       <c r="C3" t="n">
-        <v>6709</v>
+        <v>3877</v>
       </c>
       <c r="D3" t="n">
-        <v>14086</v>
+        <v>12738</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2374</v>
+        <v>1433</v>
       </c>
       <c r="C4" t="n">
-        <v>6835</v>
+        <v>7518</v>
       </c>
       <c r="D4" t="n">
-        <v>7095</v>
+        <v>7603</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1707</v>
+        <v>838</v>
       </c>
       <c r="C5" t="n">
-        <v>5082</v>
+        <v>7377</v>
       </c>
       <c r="D5" t="n">
-        <v>2736</v>
+        <v>2652</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1111</v>
+        <v>381</v>
       </c>
       <c r="C6" t="n">
-        <v>4240</v>
+        <v>3950</v>
       </c>
       <c r="D6" t="n">
-        <v>1175</v>
+        <v>922</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>595</v>
+        <v>147</v>
       </c>
       <c r="C7" t="n">
-        <v>3291</v>
+        <v>1435</v>
       </c>
       <c r="D7" t="n">
-        <v>685</v>
+        <v>517</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>254</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>1944</v>
+        <v>515</v>
       </c>
       <c r="D8" t="n">
-        <v>446</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>93</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>843</v>
+        <v>312</v>
       </c>
       <c r="D9" t="n">
-        <v>315</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>333</v>
+        <v>239</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
         <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8238</v>
+        <v>551</v>
       </c>
       <c r="C2" t="n">
-        <v>17924</v>
+        <v>2085</v>
       </c>
       <c r="D2" t="n">
-        <v>20012</v>
+        <v>8556</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3502</v>
+        <v>1250</v>
       </c>
       <c r="C3" t="n">
-        <v>7889</v>
+        <v>4115</v>
       </c>
       <c r="D3" t="n">
-        <v>13517</v>
+        <v>12389</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2283</v>
+        <v>1560</v>
       </c>
       <c r="C4" t="n">
-        <v>6575</v>
+        <v>6757</v>
       </c>
       <c r="D4" t="n">
-        <v>7886</v>
+        <v>8279</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1748</v>
+        <v>833</v>
       </c>
       <c r="C5" t="n">
-        <v>5634</v>
+        <v>8361</v>
       </c>
       <c r="D5" t="n">
-        <v>3212</v>
+        <v>2992</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1224</v>
+        <v>304</v>
       </c>
       <c r="C6" t="n">
-        <v>4534</v>
+        <v>4934</v>
       </c>
       <c r="D6" t="n">
-        <v>1369</v>
+        <v>938</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>712</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>3620</v>
+        <v>1340</v>
       </c>
       <c r="D7" t="n">
-        <v>733</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>340</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>2425</v>
+        <v>482</v>
       </c>
       <c r="D8" t="n">
-        <v>467</v>
+        <v>438</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>1233</v>
+        <v>234</v>
       </c>
       <c r="D9" t="n">
-        <v>328</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>512</v>
+        <v>184</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>234</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7403</v>
+        <v>1007</v>
       </c>
       <c r="C2" t="n">
-        <v>12475</v>
+        <v>7546</v>
       </c>
       <c r="D2" t="n">
-        <v>16658</v>
+        <v>9088</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4123</v>
+        <v>805</v>
       </c>
       <c r="C3" t="n">
-        <v>12277</v>
+        <v>2734</v>
       </c>
       <c r="D3" t="n">
-        <v>14750</v>
+        <v>11053</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1615</v>
+        <v>1255</v>
       </c>
       <c r="C4" t="n">
-        <v>8880</v>
+        <v>5311</v>
       </c>
       <c r="D4" t="n">
-        <v>7368</v>
+        <v>8737</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1130</v>
+        <v>1031</v>
       </c>
       <c r="C5" t="n">
-        <v>4443</v>
+        <v>7482</v>
       </c>
       <c r="D5" t="n">
-        <v>2205</v>
+        <v>3763</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>657</v>
+        <v>466</v>
       </c>
       <c r="C6" t="n">
-        <v>3547</v>
+        <v>6512</v>
       </c>
       <c r="D6" t="n">
-        <v>718</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>314</v>
+        <v>134</v>
       </c>
       <c r="C7" t="n">
-        <v>2376</v>
+        <v>2950</v>
       </c>
       <c r="D7" t="n">
-        <v>457</v>
+        <v>602</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>121</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>1208</v>
+        <v>840</v>
       </c>
       <c r="D8" t="n">
-        <v>321</v>
+        <v>446</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>501</v>
+        <v>328</v>
       </c>
       <c r="D9" t="n">
-        <v>244</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>229</v>
+        <v>206</v>
       </c>
       <c r="D10" t="n">
-        <v>203</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>158</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4295</v>
+        <v>558</v>
       </c>
       <c r="C2" t="n">
-        <v>5709</v>
+        <v>5132</v>
       </c>
       <c r="D2" t="n">
-        <v>11726</v>
+        <v>7333</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4663</v>
+        <v>768</v>
       </c>
       <c r="C3" t="n">
-        <v>11236</v>
+        <v>4409</v>
       </c>
       <c r="D3" t="n">
-        <v>14168</v>
+        <v>10255</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2204</v>
+        <v>1020</v>
       </c>
       <c r="C4" t="n">
-        <v>10569</v>
+        <v>4190</v>
       </c>
       <c r="D4" t="n">
-        <v>8348</v>
+        <v>8888</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1249</v>
+        <v>1079</v>
       </c>
       <c r="C5" t="n">
-        <v>6310</v>
+        <v>6666</v>
       </c>
       <c r="D5" t="n">
-        <v>2775</v>
+        <v>4341</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>770</v>
+        <v>581</v>
       </c>
       <c r="C6" t="n">
-        <v>4022</v>
+        <v>7188</v>
       </c>
       <c r="D6" t="n">
-        <v>858</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>291</v>
+        <v>146</v>
       </c>
       <c r="C7" t="n">
-        <v>2882</v>
+        <v>4163</v>
       </c>
       <c r="D7" t="n">
-        <v>495</v>
+        <v>662</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1553</v>
+        <v>1330</v>
       </c>
       <c r="D8" t="n">
-        <v>330</v>
+        <v>479</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>537</v>
+        <v>430</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>208</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>183</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3862</v>
+        <v>518</v>
       </c>
       <c r="C2" t="n">
-        <v>10389</v>
+        <v>9099</v>
       </c>
       <c r="D2" t="n">
-        <v>15773</v>
+        <v>8510</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3792</v>
+        <v>575</v>
       </c>
       <c r="C3" t="n">
-        <v>7784</v>
+        <v>4211</v>
       </c>
       <c r="D3" t="n">
-        <v>12883</v>
+        <v>9168</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2772</v>
+        <v>800</v>
       </c>
       <c r="C4" t="n">
-        <v>10662</v>
+        <v>4205</v>
       </c>
       <c r="D4" t="n">
-        <v>9044</v>
+        <v>8840</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1456</v>
+        <v>978</v>
       </c>
       <c r="C5" t="n">
-        <v>8100</v>
+        <v>5410</v>
       </c>
       <c r="D5" t="n">
-        <v>3546</v>
+        <v>4907</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>883</v>
+        <v>714</v>
       </c>
       <c r="C6" t="n">
-        <v>5012</v>
+        <v>6965</v>
       </c>
       <c r="D6" t="n">
-        <v>1122</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>416</v>
+        <v>267</v>
       </c>
       <c r="C7" t="n">
-        <v>3350</v>
+        <v>5406</v>
       </c>
       <c r="D7" t="n">
-        <v>539</v>
+        <v>770</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>144</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>2088</v>
+        <v>2453</v>
       </c>
       <c r="D8" t="n">
-        <v>350</v>
+        <v>497</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>915</v>
+        <v>760</v>
       </c>
       <c r="D9" t="n">
-        <v>261</v>
+        <v>386</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>336</v>
+        <v>293</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2338</v>
+        <v>352</v>
       </c>
       <c r="C2" t="n">
-        <v>5008</v>
+        <v>4804</v>
       </c>
       <c r="D2" t="n">
-        <v>11001</v>
+        <v>6196</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3677</v>
+        <v>776</v>
       </c>
       <c r="C3" t="n">
-        <v>8405</v>
+        <v>5870</v>
       </c>
       <c r="D3" t="n">
-        <v>12894</v>
+        <v>9838</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3045</v>
+        <v>1297</v>
       </c>
       <c r="C4" t="n">
-        <v>10579</v>
+        <v>6137</v>
       </c>
       <c r="D4" t="n">
-        <v>9602</v>
+        <v>9145</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1522</v>
+        <v>722</v>
       </c>
       <c r="C5" t="n">
-        <v>9982</v>
+        <v>8926</v>
       </c>
       <c r="D5" t="n">
-        <v>3728</v>
+        <v>4534</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>727</v>
+        <v>246</v>
       </c>
       <c r="C6" t="n">
-        <v>5868</v>
+        <v>6936</v>
       </c>
       <c r="D6" t="n">
-        <v>1099</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>133</v>
+        <v>68</v>
       </c>
       <c r="C7" t="n">
-        <v>3619</v>
+        <v>2403</v>
       </c>
       <c r="D7" t="n">
-        <v>547</v>
+        <v>592</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>1490</v>
+        <v>744</v>
       </c>
       <c r="D8" t="n">
-        <v>371</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>329</v>
+        <v>287</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>162</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2463</v>
+        <v>256</v>
       </c>
       <c r="C2" t="n">
-        <v>8080</v>
+        <v>3122</v>
       </c>
       <c r="D2" t="n">
-        <v>10866</v>
+        <v>5311</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2703</v>
+        <v>512</v>
       </c>
       <c r="C3" t="n">
-        <v>6199</v>
+        <v>4725</v>
       </c>
       <c r="D3" t="n">
-        <v>11805</v>
+        <v>8608</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2871</v>
+        <v>884</v>
       </c>
       <c r="C4" t="n">
-        <v>9378</v>
+        <v>5640</v>
       </c>
       <c r="D4" t="n">
-        <v>9815</v>
+        <v>8623</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1866</v>
+        <v>682</v>
       </c>
       <c r="C5" t="n">
-        <v>10128</v>
+        <v>6761</v>
       </c>
       <c r="D5" t="n">
-        <v>4460</v>
+        <v>4679</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>925</v>
+        <v>247</v>
       </c>
       <c r="C6" t="n">
-        <v>7532</v>
+        <v>6463</v>
       </c>
       <c r="D6" t="n">
-        <v>1448</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>266</v>
+        <v>57</v>
       </c>
       <c r="C7" t="n">
-        <v>4548</v>
+        <v>3093</v>
       </c>
       <c r="D7" t="n">
-        <v>606</v>
+        <v>574</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>2248</v>
+        <v>878</v>
       </c>
       <c r="D8" t="n">
-        <v>389</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>691</v>
+        <v>272</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>125</v>
       </c>
       <c r="D10" t="n">
-        <v>171</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1676</v>
+        <v>184</v>
       </c>
       <c r="C2" t="n">
-        <v>4207</v>
+        <v>9794</v>
       </c>
       <c r="D2" t="n">
-        <v>7737</v>
+        <v>10025</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2308</v>
+        <v>329</v>
       </c>
       <c r="C3" t="n">
-        <v>6285</v>
+        <v>3353</v>
       </c>
       <c r="D3" t="n">
-        <v>11076</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2601</v>
+        <v>619</v>
       </c>
       <c r="C4" t="n">
-        <v>8232</v>
+        <v>5067</v>
       </c>
       <c r="D4" t="n">
-        <v>9859</v>
+        <v>8275</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2023</v>
+        <v>704</v>
       </c>
       <c r="C5" t="n">
-        <v>9957</v>
+        <v>6028</v>
       </c>
       <c r="D5" t="n">
-        <v>4975</v>
+        <v>5256</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1068</v>
+        <v>403</v>
       </c>
       <c r="C6" t="n">
-        <v>8600</v>
+        <v>6606</v>
       </c>
       <c r="D6" t="n">
-        <v>1690</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>237</v>
+        <v>122</v>
       </c>
       <c r="C7" t="n">
-        <v>5530</v>
+        <v>4743</v>
       </c>
       <c r="D7" t="n">
-        <v>670</v>
+        <v>753</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="C8" t="n">
-        <v>2808</v>
+        <v>1928</v>
       </c>
       <c r="D8" t="n">
-        <v>404</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>749</v>
+        <v>541</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>227</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2231</v>
+        <v>216</v>
       </c>
       <c r="C2" t="n">
-        <v>9987</v>
+        <v>7064</v>
       </c>
       <c r="D2" t="n">
-        <v>15302</v>
+        <v>8489</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1767</v>
+        <v>221</v>
       </c>
       <c r="C3" t="n">
-        <v>4913</v>
+        <v>5665</v>
       </c>
       <c r="D3" t="n">
-        <v>10010</v>
+        <v>7381</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2197</v>
+        <v>429</v>
       </c>
       <c r="C4" t="n">
-        <v>7275</v>
+        <v>4089</v>
       </c>
       <c r="D4" t="n">
-        <v>9722</v>
+        <v>7896</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2014</v>
+        <v>611</v>
       </c>
       <c r="C5" t="n">
-        <v>9087</v>
+        <v>5432</v>
       </c>
       <c r="D5" t="n">
-        <v>5385</v>
+        <v>5538</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1272</v>
+        <v>487</v>
       </c>
       <c r="C6" t="n">
-        <v>9026</v>
+        <v>6266</v>
       </c>
       <c r="D6" t="n">
-        <v>2078</v>
+        <v>2652</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>425</v>
+        <v>216</v>
       </c>
       <c r="C7" t="n">
-        <v>6665</v>
+        <v>5599</v>
       </c>
       <c r="D7" t="n">
-        <v>783</v>
+        <v>969</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>3687</v>
+        <v>3168</v>
       </c>
       <c r="D8" t="n">
-        <v>428</v>
+        <v>413</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>1381</v>
+        <v>1125</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>372</v>
+        <v>329</v>
       </c>
       <c r="D10" t="n">
-        <v>184</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5636</v>
+        <v>3863</v>
       </c>
       <c r="C2" t="n">
-        <v>14138</v>
+        <v>8667</v>
       </c>
       <c r="D2" t="n">
-        <v>7252</v>
+        <v>5323</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1649</v>
+        <v>333</v>
       </c>
       <c r="C2" t="n">
-        <v>5913</v>
+        <v>7156</v>
       </c>
       <c r="D2" t="n">
-        <v>11384</v>
+        <v>12411</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2397</v>
+        <v>182</v>
       </c>
       <c r="C3" t="n">
-        <v>6556</v>
+        <v>5540</v>
       </c>
       <c r="D3" t="n">
-        <v>11213</v>
+        <v>7038</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2984</v>
+        <v>301</v>
       </c>
       <c r="C4" t="n">
-        <v>10274</v>
+        <v>4730</v>
       </c>
       <c r="D4" t="n">
-        <v>9930</v>
+        <v>7501</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1175</v>
+        <v>494</v>
       </c>
       <c r="C5" t="n">
-        <v>13012</v>
+        <v>4673</v>
       </c>
       <c r="D5" t="n">
-        <v>4864</v>
+        <v>5731</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>392</v>
+        <v>501</v>
       </c>
       <c r="C6" t="n">
-        <v>8035</v>
+        <v>5846</v>
       </c>
       <c r="D6" t="n">
-        <v>1673</v>
+        <v>3006</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>80</v>
+        <v>289</v>
       </c>
       <c r="C7" t="n">
-        <v>3613</v>
+        <v>5877</v>
       </c>
       <c r="D7" t="n">
-        <v>511</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="C8" t="n">
-        <v>1353</v>
+        <v>4112</v>
       </c>
       <c r="D8" t="n">
-        <v>290</v>
+        <v>485</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>364</v>
+        <v>1925</v>
       </c>
       <c r="D9" t="n">
-        <v>180</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>147</v>
+        <v>625</v>
       </c>
       <c r="D10" t="n">
-        <v>133</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>85</v>
+        <v>198</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7286</v>
+        <v>4100</v>
       </c>
       <c r="C2" t="n">
-        <v>9163</v>
+        <v>14492</v>
       </c>
       <c r="D2" t="n">
-        <v>12195</v>
+        <v>18138</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2395</v>
+        <v>1277</v>
       </c>
       <c r="C3" t="n">
-        <v>7125</v>
+        <v>3422</v>
       </c>
       <c r="D3" t="n">
-        <v>1857</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4892</v>
+        <v>3773</v>
       </c>
       <c r="C2" t="n">
-        <v>9527</v>
+        <v>6455</v>
       </c>
       <c r="D2" t="n">
-        <v>15309</v>
+        <v>29688</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3972</v>
+        <v>2271</v>
       </c>
       <c r="C3" t="n">
-        <v>7139</v>
+        <v>8685</v>
       </c>
       <c r="D3" t="n">
-        <v>3457</v>
+        <v>4203</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1075</v>
+        <v>616</v>
       </c>
       <c r="C4" t="n">
-        <v>4218</v>
+        <v>2182</v>
       </c>
       <c r="D4" t="n">
-        <v>1555</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>135</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>327</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4034</v>
+        <v>2020</v>
       </c>
       <c r="C2" t="n">
-        <v>7250</v>
+        <v>7688</v>
       </c>
       <c r="D2" t="n">
-        <v>17003</v>
+        <v>26514</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3677</v>
+        <v>2498</v>
       </c>
       <c r="C3" t="n">
-        <v>7298</v>
+        <v>6369</v>
       </c>
       <c r="D3" t="n">
-        <v>5104</v>
+        <v>8175</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2109</v>
+        <v>1268</v>
       </c>
       <c r="C4" t="n">
-        <v>5756</v>
+        <v>6007</v>
       </c>
       <c r="D4" t="n">
-        <v>1872</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>493</v>
+        <v>310</v>
       </c>
       <c r="C5" t="n">
-        <v>2363</v>
+        <v>1339</v>
       </c>
       <c r="D5" t="n">
-        <v>1215</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>261</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>115</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>334</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>287</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4775</v>
+        <v>1634</v>
       </c>
       <c r="C2" t="n">
-        <v>4571</v>
+        <v>5516</v>
       </c>
       <c r="D2" t="n">
-        <v>25187</v>
+        <v>25827</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3176</v>
+        <v>1877</v>
       </c>
       <c r="C3" t="n">
-        <v>6342</v>
+        <v>6135</v>
       </c>
       <c r="D3" t="n">
-        <v>6553</v>
+        <v>10520</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2447</v>
+        <v>1615</v>
       </c>
       <c r="C4" t="n">
-        <v>6450</v>
+        <v>6087</v>
       </c>
       <c r="D4" t="n">
-        <v>2404</v>
+        <v>3052</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1050</v>
+        <v>662</v>
       </c>
       <c r="C5" t="n">
-        <v>4017</v>
+        <v>3865</v>
       </c>
       <c r="D5" t="n">
-        <v>1279</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>276</v>
+        <v>189</v>
       </c>
       <c r="C6" t="n">
-        <v>1328</v>
+        <v>827</v>
       </c>
       <c r="D6" t="n">
-        <v>948</v>
+        <v>833</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>356</v>
+        <v>295</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>375</v>
+        <v>310</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>250</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>157</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5591</v>
+        <v>2613</v>
       </c>
       <c r="C2" t="n">
-        <v>7810</v>
+        <v>9241</v>
       </c>
       <c r="D2" t="n">
-        <v>27263</v>
+        <v>23448</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2858</v>
+        <v>1464</v>
       </c>
       <c r="C3" t="n">
-        <v>4526</v>
+        <v>5077</v>
       </c>
       <c r="D3" t="n">
-        <v>8253</v>
+        <v>12106</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1727</v>
+        <v>1506</v>
       </c>
       <c r="C4" t="n">
-        <v>5174</v>
+        <v>5927</v>
       </c>
       <c r="D4" t="n">
-        <v>2634</v>
+        <v>4321</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>906</v>
+        <v>954</v>
       </c>
       <c r="C5" t="n">
-        <v>3832</v>
+        <v>4936</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>306</v>
+        <v>366</v>
       </c>
       <c r="C6" t="n">
-        <v>1761</v>
+        <v>2334</v>
       </c>
       <c r="D6" t="n">
-        <v>754</v>
+        <v>881</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="C7" t="n">
-        <v>524</v>
+        <v>555</v>
       </c>
       <c r="D7" t="n">
-        <v>522</v>
+        <v>620</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>302</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>197</v>
+        <v>274</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4664</v>
+        <v>2775</v>
       </c>
       <c r="C2" t="n">
-        <v>10685</v>
+        <v>8558</v>
       </c>
       <c r="D2" t="n">
-        <v>30453</v>
+        <v>23249</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3494</v>
+        <v>1609</v>
       </c>
       <c r="C3" t="n">
-        <v>5524</v>
+        <v>6183</v>
       </c>
       <c r="D3" t="n">
-        <v>10839</v>
+        <v>12906</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2001</v>
+        <v>1280</v>
       </c>
       <c r="C4" t="n">
-        <v>4680</v>
+        <v>5379</v>
       </c>
       <c r="D4" t="n">
-        <v>3686</v>
+        <v>5534</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1171</v>
+        <v>1067</v>
       </c>
       <c r="C5" t="n">
-        <v>4525</v>
+        <v>5309</v>
       </c>
       <c r="D5" t="n">
-        <v>1397</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="C6" t="n">
-        <v>2893</v>
+        <v>3486</v>
       </c>
       <c r="D6" t="n">
-        <v>821</v>
+        <v>948</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>179</v>
+        <v>207</v>
       </c>
       <c r="C7" t="n">
-        <v>1197</v>
+        <v>1374</v>
       </c>
       <c r="D7" t="n">
-        <v>559</v>
+        <v>654</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="C8" t="n">
-        <v>384</v>
+        <v>413</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>283</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>240</v>
       </c>
       <c r="D10" t="n">
-        <v>234</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>151</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>144</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4649</v>
+        <v>2494</v>
       </c>
       <c r="C2" t="n">
-        <v>11667</v>
+        <v>5340</v>
       </c>
       <c r="D2" t="n">
-        <v>26475</v>
+        <v>18475</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3338</v>
+        <v>2187</v>
       </c>
       <c r="C3" t="n">
-        <v>7152</v>
+        <v>9300</v>
       </c>
       <c r="D3" t="n">
-        <v>13057</v>
+        <v>14054</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2349</v>
+        <v>985</v>
       </c>
       <c r="C4" t="n">
-        <v>5044</v>
+        <v>8401</v>
       </c>
       <c r="D4" t="n">
-        <v>4843</v>
+        <v>5033</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1379</v>
+        <v>515</v>
       </c>
       <c r="C5" t="n">
-        <v>4469</v>
+        <v>3416</v>
       </c>
       <c r="D5" t="n">
-        <v>1772</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>777</v>
+        <v>191</v>
       </c>
       <c r="C6" t="n">
-        <v>3706</v>
+        <v>1346</v>
       </c>
       <c r="D6" t="n">
-        <v>901</v>
+        <v>640</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>314</v>
+        <v>91</v>
       </c>
       <c r="C7" t="n">
-        <v>2060</v>
+        <v>404</v>
       </c>
       <c r="D7" t="n">
-        <v>599</v>
+        <v>446</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>778</v>
+        <v>277</v>
       </c>
       <c r="D8" t="n">
-        <v>401</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>292</v>
+        <v>235</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6518,10 +6518,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
         <v>158</v>
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>144</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
